--- a/public/assets/BOs/Odin.xlsx
+++ b/public/assets/BOs/Odin.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\OneDrive\Github\DoD\DeitiesOfDeath\public\assets\BOs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\doc\coding\DoD\DeitiesOfDeath\public\assets\BOs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4745D38-D60B-4B85-A693-63EDEB1C2B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E621E81-55FB-4F65-9DCA-34A7DC0D2502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4500" yWindow="4635" windowWidth="43200" windowHeight="23445" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil7" sheetId="8" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Feuil2" sheetId="3" r:id="rId3"/>
     <sheet name="Feuil4" sheetId="5" r:id="rId4"/>
     <sheet name="Feuil5" sheetId="6" r:id="rId5"/>
-    <sheet name="Feuil6" sheetId="7" r:id="rId6"/>
+    <sheet name="Feuil8" sheetId="9" r:id="rId6"/>
     <sheet name="Feuil3" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
@@ -2161,9 +2161,6 @@
     </r>
   </si>
   <si>
-    <t>Odin special anatolia build - DoD Léonce</t>
-  </si>
-  <si>
     <t>build dock and Auto-Queue Fishing Ships you want 3/4 fish before second dock</t>
   </si>
   <si>
@@ -2177,6 +2174,9 @@
   </si>
   <si>
     <t>if you go land, military building then fishing boat upgrd</t>
+  </si>
+  <si>
+    <t>Special anatolia build - By Léonce</t>
   </si>
 </sst>
 </file>
@@ -2800,7 +2800,7 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2855,9 +2855,6 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="25" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="25"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="25" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="25" applyFont="1"/>
@@ -2887,6 +2884,28 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="25" applyFont="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="46" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2928,47 +2947,48 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="4" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="25" applyFont="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="25" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="25" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="14" fontId="47" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="47" fillId="14" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="46" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="24" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="25" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2987,8 +3007,8 @@
     <cellStyle name="Heading 1 14" xfId="17" xr:uid="{EA71912F-23DC-4619-968E-43C15F9C609B}"/>
     <cellStyle name="Heading 13" xfId="18" xr:uid="{4443B8FA-E05B-49A9-B2AF-81F7D84CBA32}"/>
     <cellStyle name="Heading 2 15" xfId="19" xr:uid="{CE7BA955-1964-42BE-A167-47B48C6C907A}"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Hyperlink 2" xfId="20" xr:uid="{D2C2A2EE-AD60-418D-BBD6-29D931331F72}"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Lien hypertexte 2" xfId="3" xr:uid="{61732208-7CA0-4B11-A373-9A79B6EA098D}"/>
     <cellStyle name="Lien hypertexte 3" xfId="7" xr:uid="{9783B941-0010-482A-9D19-1A49087C996A}"/>
     <cellStyle name="Neutral 16" xfId="21" xr:uid="{C34E335D-3673-435D-880A-D823A99428F7}"/>
@@ -3282,200 +3302,200 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B47CA131-95F3-4EFC-BDE4-73DAA8914DBA}">
   <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" customWidth="1"/>
-    <col min="2" max="2" width="50.42578125" customWidth="1"/>
-    <col min="3" max="3" width="62.5703125" customWidth="1"/>
+    <col min="1" max="1" width="32.33203125" customWidth="1"/>
+    <col min="2" max="2" width="50.44140625" customWidth="1"/>
+    <col min="3" max="3" width="62.5546875" customWidth="1"/>
     <col min="4" max="4" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:4" ht="18">
+      <c r="A1" s="57" t="s">
         <v>192</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="48" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.6">
+      <c r="A2" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-    </row>
-    <row r="3" spans="1:4" ht="15">
-      <c r="A3" s="34" t="s">
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+    </row>
+    <row r="3" spans="1:4" ht="14.4">
+      <c r="A3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-    </row>
-    <row r="4" spans="1:4" ht="30">
-      <c r="A4" s="35" t="s">
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+    </row>
+    <row r="4" spans="1:4" ht="28.8">
+      <c r="A4" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="35" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="36" t="s">
         <v>171</v>
       </c>
-      <c r="D4" s="34"/>
-    </row>
-    <row r="5" spans="1:4" ht="15">
-      <c r="A5" s="35" t="s">
+      <c r="D4" s="33"/>
+    </row>
+    <row r="5" spans="1:4" ht="14.4">
+      <c r="A5" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="36" t="s">
         <v>173</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="D5" s="34"/>
-    </row>
-    <row r="6" spans="1:4" ht="15">
-      <c r="A6" s="35" t="s">
+      <c r="D5" s="33"/>
+    </row>
+    <row r="6" spans="1:4" ht="14.4">
+      <c r="A6" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-    </row>
-    <row r="7" spans="1:4" ht="15">
-      <c r="A7" s="35" t="s">
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+    </row>
+    <row r="7" spans="1:4" ht="14.4">
+      <c r="A7" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="36" t="s">
         <v>177</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="33" t="s">
         <v>178</v>
       </c>
-      <c r="D7" s="34"/>
-    </row>
-    <row r="8" spans="1:4" ht="15">
-      <c r="A8" s="35" t="s">
+      <c r="D7" s="33"/>
+    </row>
+    <row r="8" spans="1:4" ht="14.4">
+      <c r="A8" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-    </row>
-    <row r="9" spans="1:4" ht="15">
-      <c r="A9" s="35" t="s">
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+    </row>
+    <row r="9" spans="1:4" ht="14.4">
+      <c r="A9" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="D9" s="34"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="49" t="s">
+      <c r="D9" s="33"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.6">
+      <c r="A10" s="60" t="s">
         <v>183</v>
       </c>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-    </row>
-    <row r="11" spans="1:4" s="34" customFormat="1" ht="15">
-      <c r="A11" s="34" t="s">
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+    </row>
+    <row r="11" spans="1:4" s="33" customFormat="1" ht="14.4">
+      <c r="A11" s="33" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15">
-      <c r="A12" s="37" t="s">
+    <row r="12" spans="1:4" ht="14.4">
+      <c r="A12" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="C12" s="37" t="s">
+      <c r="C12" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="D12" s="34"/>
-    </row>
-    <row r="13" spans="1:4" ht="15">
-      <c r="A13" s="34"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-    </row>
-    <row r="14" spans="1:4" ht="15">
-      <c r="A14" s="38"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="49" t="s">
+      <c r="D12" s="33"/>
+    </row>
+    <row r="13" spans="1:4" ht="14.4">
+      <c r="A13" s="33"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+    </row>
+    <row r="14" spans="1:4" ht="14.4">
+      <c r="A14" s="37"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+    </row>
+    <row r="15" spans="1:4" ht="15.6">
+      <c r="A15" s="60" t="s">
         <v>187</v>
       </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-    </row>
-    <row r="16" spans="1:4" ht="15">
-      <c r="A16" s="34" t="s">
+      <c r="B15" s="58"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+    </row>
+    <row r="16" spans="1:4" ht="14.4">
+      <c r="A16" s="33" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15">
-      <c r="A17" s="37" t="s">
+    <row r="17" spans="1:4" ht="14.4">
+      <c r="A17" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="39" t="s">
         <v>189</v>
       </c>
-      <c r="C17" s="40" t="s">
+      <c r="C17" s="39" t="s">
         <v>190</v>
       </c>
-      <c r="D17" s="41"/>
-    </row>
-    <row r="18" spans="1:4" ht="15">
-      <c r="C18" s="42"/>
-    </row>
-    <row r="19" spans="1:4" ht="15">
+      <c r="D17" s="40"/>
+    </row>
+    <row r="18" spans="1:4" ht="14.4">
+      <c r="C18" s="41"/>
+    </row>
+    <row r="19" spans="1:4" ht="14.4">
       <c r="A19" s="22" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15">
-      <c r="A20" s="50"/>
-      <c r="B20" s="47"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="43"/>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="43"/>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="43"/>
-      <c r="B23" s="44"/>
-    </row>
-    <row r="24" spans="1:4" ht="15">
-      <c r="A24" s="45"/>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="44"/>
-    </row>
-    <row r="26" spans="1:4" ht="15">
-      <c r="A26" s="45"/>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="44"/>
+    <row r="20" spans="1:4" ht="14.4">
+      <c r="A20" s="61"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.6">
+      <c r="A21" s="42"/>
+    </row>
+    <row r="22" spans="1:4" ht="15.6">
+      <c r="A22" s="42"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.6">
+      <c r="A23" s="42"/>
+      <c r="B23" s="43"/>
+    </row>
+    <row r="24" spans="1:4" ht="14.4">
+      <c r="A24" s="44"/>
+    </row>
+    <row r="25" spans="1:4" ht="15.6">
+      <c r="A25" s="43"/>
+    </row>
+    <row r="26" spans="1:4" ht="14.4">
+      <c r="A26" s="44"/>
+    </row>
+    <row r="27" spans="1:4" ht="15.6">
+      <c r="A27" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3492,25 +3512,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2ADDC42-BEB8-4B0C-8D96-AA8F9BC1E623}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" thickBot="1">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:4" ht="18" thickBot="1">
+      <c r="A1" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="53"/>
-    </row>
-    <row r="2" spans="1:4" ht="16.5" thickBot="1">
-      <c r="A2" s="54" t="s">
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="64"/>
+    </row>
+    <row r="2" spans="1:4" ht="16.2" thickBot="1">
+      <c r="A2" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="56"/>
-    </row>
-    <row r="3" spans="1:4" ht="58.5" thickBot="1">
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="67"/>
+    </row>
+    <row r="3" spans="1:4" ht="56.4" thickBot="1">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -3518,7 +3538,7 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4" ht="87" thickBot="1">
+    <row r="4" spans="1:4" ht="70.2" thickBot="1">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -3530,7 +3550,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="30" thickBot="1">
+    <row r="5" spans="1:4" ht="28.8" thickBot="1">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -3540,7 +3560,7 @@
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:4" ht="72.75" thickBot="1">
+    <row r="6" spans="1:4" ht="56.4" thickBot="1">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -3552,7 +3572,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" ht="30" thickBot="1">
+    <row r="7" spans="1:4" ht="28.8" thickBot="1">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
@@ -3562,7 +3582,7 @@
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:4" ht="30" thickBot="1">
+    <row r="8" spans="1:4" ht="28.8" thickBot="1">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -3572,7 +3592,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" ht="44.25" thickBot="1">
+    <row r="9" spans="1:4" ht="28.8" thickBot="1">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -3584,7 +3604,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="30" thickBot="1">
+    <row r="10" spans="1:4" ht="28.8" thickBot="1">
       <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
@@ -3594,7 +3614,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" ht="44.25" thickBot="1">
+    <row r="11" spans="1:4" ht="42.6" thickBot="1">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -3606,7 +3626,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:4" ht="44.25" thickBot="1">
+    <row r="12" spans="1:4" ht="42.6" thickBot="1">
       <c r="A12" s="3" t="s">
         <v>17</v>
       </c>
@@ -3618,7 +3638,7 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" ht="30" thickBot="1">
+    <row r="13" spans="1:4" ht="28.8" thickBot="1">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -3628,7 +3648,7 @@
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:4" ht="30" thickBot="1">
+    <row r="14" spans="1:4" ht="28.8" thickBot="1">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
@@ -3638,15 +3658,15 @@
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:4" ht="16.5" thickBot="1">
-      <c r="A15" s="54" t="s">
+    <row r="15" spans="1:4" ht="16.2" thickBot="1">
+      <c r="A15" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="56"/>
-    </row>
-    <row r="16" spans="1:4" ht="58.5" thickBot="1">
+      <c r="B15" s="66"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="67"/>
+    </row>
+    <row r="16" spans="1:4" ht="56.4" thickBot="1">
       <c r="A16" s="1" t="s">
         <v>2</v>
       </c>
@@ -3654,7 +3674,7 @@
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="1:4" ht="52.5" thickBot="1">
+    <row r="17" spans="1:4" ht="54" thickBot="1">
       <c r="A17" s="3" t="s">
         <v>22</v>
       </c>
@@ -3668,15 +3688,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="16.5" thickBot="1">
-      <c r="A18" s="54" t="s">
+    <row r="18" spans="1:4" ht="16.2" thickBot="1">
+      <c r="A18" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="55"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="56"/>
-    </row>
-    <row r="19" spans="1:4" ht="58.5" thickBot="1">
+      <c r="B18" s="66"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="67"/>
+    </row>
+    <row r="19" spans="1:4" ht="56.4" thickBot="1">
       <c r="A19" s="1" t="s">
         <v>2</v>
       </c>
@@ -3684,7 +3704,7 @@
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="1:4" ht="44.25" thickBot="1">
+    <row r="20" spans="1:4" ht="42.6" thickBot="1">
       <c r="A20" s="1" t="s">
         <v>25</v>
       </c>
@@ -3716,23 +3736,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B0C65D-747D-4450-97BA-4845EDE66ADE}">
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="18">
-      <c r="A1" s="58" t="s">
+    <row r="1" spans="1:4" ht="17.399999999999999">
+      <c r="A1" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-    </row>
-    <row r="2" spans="1:4" ht="18">
-      <c r="A2" s="59" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+    </row>
+    <row r="2" spans="1:4" ht="17.399999999999999">
+      <c r="A2" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
@@ -3836,13 +3856,13 @@
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
     </row>
-    <row r="13" spans="1:4" ht="18">
-      <c r="A13" s="59" t="s">
+    <row r="13" spans="1:4" ht="17.399999999999999">
+      <c r="A13" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="59"/>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="5" t="s">
@@ -3866,13 +3886,13 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="18">
-      <c r="A16" s="59" t="s">
+    <row r="16" spans="1:4" ht="17.399999999999999">
+      <c r="A16" s="70" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="59"/>
-      <c r="C16" s="59"/>
-      <c r="D16" s="59"/>
+      <c r="B16" s="70"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="70"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="7" t="s">
@@ -3893,10 +3913,10 @@
       <c r="B18" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="60" t="s">
+      <c r="C18" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="60"/>
+      <c r="D18" s="71"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="7" t="s">
@@ -3905,8 +3925,8 @@
       <c r="B19" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="7" t="s">
@@ -3921,18 +3941,18 @@
       <c r="D20" s="7"/>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="57" t="s">
+      <c r="A21" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="B21" s="57"/>
-      <c r="C21" s="57"/>
-      <c r="D21" s="57"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="57"/>
-      <c r="B22" s="57"/>
-      <c r="C22" s="57"/>
-      <c r="D22" s="57"/>
+      <c r="A22" s="68"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="8"/>
@@ -3956,198 +3976,198 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD67B621-09DE-4392-B9E3-CAA83F705DF0}">
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18">
-      <c r="A1" s="65" t="s">
+    <row r="1" spans="1:4" ht="17.399999999999999">
+      <c r="A1" s="72" t="s">
         <v>193</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="66" t="s">
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.6">
+      <c r="A2" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-    </row>
-    <row r="4" spans="1:4" ht="143.25">
-      <c r="A4" s="67" t="s">
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+    </row>
+    <row r="4" spans="1:4" ht="97.2">
+      <c r="A4" s="45" t="s">
         <v>202</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="46" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="69" t="s">
+      <c r="C4" s="47" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="29.25">
-      <c r="A5" s="70" t="s">
+    <row r="5" spans="1:4">
+      <c r="A5" s="48" t="s">
         <v>203</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="68"/>
-    </row>
-    <row r="6" spans="1:4" ht="57.75">
-      <c r="A6" s="67" t="s">
+      <c r="C5" s="28"/>
+      <c r="D5" s="46"/>
+    </row>
+    <row r="6" spans="1:4" ht="28.2">
+      <c r="A6" s="45" t="s">
         <v>204</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="71" t="s">
+      <c r="D6" s="49" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="70" t="s">
+      <c r="A7" s="48" t="s">
         <v>205</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="68"/>
-    </row>
-    <row r="8" spans="1:4" ht="29.25">
-      <c r="A8" s="67" t="s">
+      <c r="C7" s="28"/>
+      <c r="D7" s="46"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="45" t="s">
         <v>206</v>
       </c>
-      <c r="B8" s="68" t="s">
+      <c r="B8" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="67" t="s">
+      <c r="A9" s="45" t="s">
         <v>207</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="45" t="s">
         <v>197</v>
       </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="67"/>
-    </row>
-    <row r="10" spans="1:4" ht="29.25">
-      <c r="A10" s="67" t="s">
+      <c r="C9" s="29"/>
+      <c r="D9" s="45"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="45" t="s">
         <v>208</v>
       </c>
-      <c r="B10" s="68" t="s">
+      <c r="B10" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67" t="s">
+      <c r="C10" s="45"/>
+      <c r="D10" s="45" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="186">
-      <c r="A11" s="70" t="s">
+    <row r="11" spans="1:4" ht="55.8">
+      <c r="A11" s="48" t="s">
         <v>209</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="67"/>
-      <c r="D11" s="68" t="s">
+      <c r="C11" s="45"/>
+      <c r="D11" s="46" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="45" t="s">
         <v>210</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="67"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="45"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="72" t="s">
+      <c r="A13" s="50" t="s">
         <v>211</v>
       </c>
-      <c r="B13" s="67" t="s">
+      <c r="B13" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-    </row>
-    <row r="14" spans="1:4" ht="15.75">
-      <c r="A14" s="66" t="s">
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+    </row>
+    <row r="14" spans="1:4" ht="15.6">
+      <c r="A14" s="73" t="s">
         <v>96</v>
       </c>
-      <c r="B14" s="66"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-    </row>
-    <row r="15" spans="1:4" ht="15.75">
-      <c r="A15" s="73"/>
-      <c r="C15" s="74" t="s">
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+    </row>
+    <row r="15" spans="1:4" ht="15.6">
+      <c r="A15" s="51"/>
+      <c r="C15" s="52" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="86.25">
-      <c r="A16" s="67" t="s">
+    <row r="16" spans="1:4" ht="55.8">
+      <c r="A16" s="45" t="s">
         <v>212</v>
       </c>
-      <c r="B16" s="75" t="s">
+      <c r="B16" s="53" t="s">
         <v>200</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="D16" s="76" t="s">
+      <c r="D16" s="54" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.75">
-      <c r="A17" s="66" t="s">
+    <row r="17" spans="1:4" ht="15.6">
+      <c r="A17" s="73" t="s">
         <v>100</v>
       </c>
-      <c r="B17" s="66"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="66"/>
-    </row>
-    <row r="18" spans="1:4" ht="129">
-      <c r="A18" s="67"/>
-      <c r="B18" s="67"/>
-      <c r="C18" s="33" t="s">
+      <c r="B17" s="73"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
+    </row>
+    <row r="18" spans="1:4" ht="42">
+      <c r="A18" s="45"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="75" t="s">
+      <c r="D18" s="53" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="171.75">
-      <c r="A19" s="67"/>
-      <c r="B19" s="77"/>
-      <c r="C19" s="78"/>
-      <c r="D19" s="68" t="s">
+    <row r="19" spans="1:4" ht="42">
+      <c r="A19" s="45"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="46" t="s">
         <v>103</v>
       </c>
     </row>
@@ -4164,24 +4184,24 @@
       <c r="D21" s="11"/>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="64"/>
-      <c r="B22" s="62"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="62"/>
-    </row>
-    <row r="23" spans="1:4" ht="15.75">
+      <c r="A22" s="74"/>
+      <c r="B22" s="75"/>
+      <c r="C22" s="75"/>
+      <c r="D22" s="75"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.6">
       <c r="A23" s="23"/>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
     </row>
-    <row r="24" spans="1:4" ht="15.75">
+    <row r="24" spans="1:4" ht="15.6">
       <c r="A24" s="23"/>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
     </row>
-    <row r="25" spans="1:4" ht="15.75">
+    <row r="25" spans="1:4" ht="15.6">
       <c r="A25" s="23"/>
       <c r="B25" s="24"/>
       <c r="C25" s="11"/>
@@ -4193,7 +4213,7 @@
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
     </row>
-    <row r="27" spans="1:4" ht="15.75">
+    <row r="27" spans="1:4" ht="15.6">
       <c r="A27" s="24"/>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -4205,7 +4225,7 @@
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
     </row>
-    <row r="29" spans="1:4" ht="15.75">
+    <row r="29" spans="1:4" ht="15.6">
       <c r="A29" s="24"/>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -4226,24 +4246,24 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB88758B-FEFF-43F0-9B74-07511A4CD275}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75">
-      <c r="A1" s="61" t="s">
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="77" t="s">
         <v>143</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
       <c r="E1" s="11"/>
     </row>
-    <row r="2" spans="1:5" ht="15.75">
-      <c r="A2" s="63" t="s">
+    <row r="2" spans="1:5" ht="15.6">
+      <c r="A2" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
       <c r="E2" s="11"/>
     </row>
     <row r="3" spans="1:5">
@@ -4257,7 +4277,7 @@
       </c>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" spans="1:5" ht="150">
+    <row r="4" spans="1:5" ht="144">
       <c r="A4" s="13" t="s">
         <v>105</v>
       </c>
@@ -4283,7 +4303,7 @@
       <c r="D5" s="12"/>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" ht="120">
+    <row r="6" spans="1:5" ht="115.2">
       <c r="A6" s="13" t="s">
         <v>110</v>
       </c>
@@ -4307,7 +4327,7 @@
       <c r="D7" s="12"/>
       <c r="E7" s="11"/>
     </row>
-    <row r="8" spans="1:5" ht="150">
+    <row r="8" spans="1:5" ht="129.6">
       <c r="A8" s="13" t="s">
         <v>113</v>
       </c>
@@ -4359,16 +4379,16 @@
       <c r="D11" s="18"/>
       <c r="E11" s="11"/>
     </row>
-    <row r="12" spans="1:5" ht="15.75">
-      <c r="A12" s="63" t="s">
+    <row r="12" spans="1:5" ht="15.6">
+      <c r="A12" s="76" t="s">
         <v>123</v>
       </c>
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="62"/>
+      <c r="B12" s="75"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="75"/>
       <c r="E12" s="11"/>
     </row>
-    <row r="13" spans="1:5" ht="75">
+    <row r="13" spans="1:5" ht="57.6">
       <c r="A13" s="12"/>
       <c r="B13" s="17"/>
       <c r="C13" s="18" t="s">
@@ -4379,7 +4399,7 @@
       </c>
       <c r="E13" s="11"/>
     </row>
-    <row r="14" spans="1:5" ht="60">
+    <row r="14" spans="1:5" ht="43.2">
       <c r="A14" s="12"/>
       <c r="B14" s="17"/>
       <c r="C14" s="18" t="s">
@@ -4388,16 +4408,16 @@
       <c r="D14" s="12"/>
       <c r="E14" s="11"/>
     </row>
-    <row r="15" spans="1:5" ht="15.75">
-      <c r="A15" s="63" t="s">
+    <row r="15" spans="1:5" ht="15.6">
+      <c r="A15" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
       <c r="E15" s="11"/>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5">
       <c r="A16" s="13" t="s">
         <v>127</v>
       </c>
@@ -4426,15 +4446,15 @@
         <v>134</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.75">
-      <c r="A18" s="63" t="s">
+    <row r="18" spans="1:4" ht="15.6">
+      <c r="A18" s="76" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="62"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-    </row>
-    <row r="19" spans="1:4" ht="315">
+      <c r="B18" s="75"/>
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
+    </row>
+    <row r="19" spans="1:4" ht="259.2">
       <c r="A19" s="23" t="s">
         <v>136</v>
       </c>
@@ -4446,21 +4466,21 @@
       </c>
       <c r="D19" s="11"/>
     </row>
-    <row r="20" spans="1:4" ht="15.75">
+    <row r="20" spans="1:4" ht="15.6">
       <c r="A20" s="23"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
     </row>
-    <row r="21" spans="1:4" ht="15.75">
-      <c r="A21" s="63" t="s">
+    <row r="21" spans="1:4" ht="15.6">
+      <c r="A21" s="76" t="s">
         <v>139</v>
       </c>
-      <c r="B21" s="62"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
-    </row>
-    <row r="22" spans="1:4" ht="192">
+      <c r="B21" s="75"/>
+      <c r="C21" s="75"/>
+      <c r="D21" s="75"/>
+    </row>
+    <row r="22" spans="1:4" ht="207">
       <c r="A22" s="25"/>
       <c r="B22" s="21"/>
       <c r="C22" s="21" t="s">
@@ -4470,7 +4490,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.75">
+    <row r="23" spans="1:4" ht="15.6">
       <c r="A23" s="24"/>
       <c r="B23" s="19"/>
       <c r="C23" s="21" t="s">
@@ -4484,7 +4504,7 @@
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
     </row>
-    <row r="25" spans="1:4" ht="15.75">
+    <row r="25" spans="1:4" ht="15.6">
       <c r="A25" s="24"/>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -4504,215 +4524,209 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A4BBB9A-43E8-4B1D-880D-828B2ACDD0BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{678F68FE-929E-4845-9B37-BCAEE1465B17}">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="64" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="18">
-      <c r="A1" s="65" t="s">
+    <row r="1" spans="1:4" ht="17.399999999999999">
+      <c r="A1" s="69" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.6">
+      <c r="A2" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="79" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+    </row>
+    <row r="4" spans="1:4" ht="163.80000000000001">
+      <c r="A4" s="79" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="80" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" s="81" t="s">
+        <v>146</v>
+      </c>
+      <c r="D4" s="82" t="s">
         <v>213</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75">
-      <c r="A2" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="67" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-    </row>
-    <row r="4" spans="1:4" ht="175.5">
-      <c r="A4" s="67" t="s">
-        <v>144</v>
-      </c>
-      <c r="B4" s="68" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="D4" s="79" t="s">
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="83" t="s">
+        <v>147</v>
+      </c>
+      <c r="B5" s="80" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="84" t="s">
+        <v>148</v>
+      </c>
+      <c r="D5" s="80"/>
+    </row>
+    <row r="6" spans="1:4" ht="28.2">
+      <c r="A6" s="79" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" s="80" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="84"/>
+      <c r="D6" s="80"/>
+    </row>
+    <row r="7" spans="1:4" ht="111">
+      <c r="A7" s="83" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" s="80" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="84"/>
+      <c r="D7" s="80" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="79" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" s="79" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="79"/>
+      <c r="D8" s="79" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="79" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="85" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="84"/>
+      <c r="D9" s="79"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="79" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" s="79" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="79"/>
+      <c r="D10" s="79" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="70" t="s">
-        <v>147</v>
-      </c>
-      <c r="B5" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="D5" s="68"/>
-    </row>
-    <row r="6" spans="1:4" ht="29.25">
-      <c r="A6" s="67" t="s">
-        <v>149</v>
-      </c>
-      <c r="B6" s="68" t="s">
+    <row r="11" spans="1:4">
+      <c r="A11" s="79" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" s="84" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="79"/>
+      <c r="D11" s="80"/>
+    </row>
+    <row r="12" spans="1:4" ht="210">
+      <c r="A12" s="79" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" s="84" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="68"/>
-    </row>
-    <row r="7" spans="1:4" ht="143.25">
-      <c r="A7" s="70" t="s">
-        <v>150</v>
-      </c>
-      <c r="B7" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="68" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="67" t="s">
-        <v>152</v>
-      </c>
-      <c r="B8" s="67" t="s">
+      <c r="C12" s="84"/>
+      <c r="D12" s="80" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="86" t="s">
+        <v>159</v>
+      </c>
+      <c r="B13" s="84" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="79"/>
+      <c r="D13" s="79"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="86" t="s">
+        <v>160</v>
+      </c>
+      <c r="B14" s="85" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="67" t="s">
-        <v>154</v>
-      </c>
-      <c r="B9" s="74" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="67"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="67" t="s">
-        <v>155</v>
-      </c>
-      <c r="B10" s="67" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67" t="s">
+      <c r="C14" s="85"/>
+      <c r="D14" s="85" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="67" t="s">
-        <v>156</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" s="67"/>
-      <c r="D11" s="68"/>
-    </row>
-    <row r="12" spans="1:4" ht="231">
-      <c r="A12" s="67" t="s">
-        <v>157</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="68" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="72" t="s">
-        <v>159</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="72" t="s">
-        <v>160</v>
-      </c>
-      <c r="B14" s="74" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="74"/>
-      <c r="D14" s="74" t="s">
+    <row r="15" spans="1:4" ht="15.6">
+      <c r="A15" s="78" t="s">
+        <v>161</v>
+      </c>
+      <c r="B15" s="78"/>
+      <c r="C15" s="78"/>
+      <c r="D15" s="78"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="87"/>
+      <c r="B16" s="85"/>
+      <c r="C16" s="85" t="s">
+        <v>162</v>
+      </c>
+      <c r="D16" s="85" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="55.8">
+      <c r="A17" s="79" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17" s="88" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="89" t="s">
+        <v>165</v>
+      </c>
+      <c r="D17" s="90" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75">
-      <c r="A15" s="66" t="s">
-        <v>161</v>
-      </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="80"/>
-      <c r="B16" s="74"/>
-      <c r="C16" s="74" t="s">
-        <v>162</v>
-      </c>
-      <c r="D16" s="74" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="57.75">
-      <c r="A17" s="67" t="s">
-        <v>164</v>
-      </c>
-      <c r="B17" s="75" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="D17" s="76" t="s">
+    <row r="18" spans="1:4" ht="15.6">
+      <c r="A18" s="78" t="s">
+        <v>166</v>
+      </c>
+      <c r="B18" s="78"/>
+      <c r="C18" s="78"/>
+      <c r="D18" s="78"/>
+    </row>
+    <row r="19" spans="1:4" ht="111">
+      <c r="A19" s="79"/>
+      <c r="B19" s="79" t="s">
+        <v>167</v>
+      </c>
+      <c r="C19" s="91" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.75">
-      <c r="A18" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="B18" s="66"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="66"/>
-    </row>
-    <row r="19" spans="1:4" ht="114.75">
-      <c r="A19" s="67"/>
-      <c r="B19" s="67" t="s">
-        <v>167</v>
-      </c>
-      <c r="C19" s="81" t="s">
-        <v>218</v>
-      </c>
-      <c r="D19" s="75" t="s">
+      <c r="D19" s="88" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4730,23 +4744,23 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8B1C384-FFE0-4A4D-8C09-0D215D36435B}">
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="18">
-      <c r="A1" s="58" t="s">
+    <row r="1" spans="1:4" ht="17.399999999999999">
+      <c r="A1" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-    </row>
-    <row r="2" spans="1:4" ht="18">
-      <c r="A2" s="59" t="s">
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+    </row>
+    <row r="2" spans="1:4" ht="17.399999999999999">
+      <c r="A2" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
@@ -4808,7 +4822,7 @@
       </c>
       <c r="D8" s="5"/>
     </row>
-    <row r="9" spans="1:4" ht="17.25">
+    <row r="9" spans="1:4" ht="16.8">
       <c r="A9" s="5" t="s">
         <v>74</v>
       </c>
@@ -4842,13 +4856,13 @@
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
     </row>
-    <row r="12" spans="1:4" ht="18">
-      <c r="A12" s="59" t="s">
+    <row r="12" spans="1:4" ht="17.399999999999999">
+      <c r="A12" s="70" t="s">
         <v>81</v>
       </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
+      <c r="B12" s="70"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="70"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
@@ -4872,13 +4886,13 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="18">
-      <c r="A15" s="59" t="s">
+    <row r="15" spans="1:4" ht="17.399999999999999">
+      <c r="A15" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="59"/>
-      <c r="D15" s="59"/>
+      <c r="B15" s="70"/>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="7" t="s">
@@ -4894,7 +4908,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="85.5">
+    <row r="17" spans="1:4" ht="82.8">
       <c r="A17" s="7" t="s">
         <v>89</v>
       </c>
